--- a/themes/mobileAppNavigation.xlsx
+++ b/themes/mobileAppNavigation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,156 +450,156 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Оплата товаров и услуг доступна на главном экране в разделе «Платежи» [«Уралсиб Онлайн»](https://uralsib.ru/online)'</t>
+          <t xml:space="preserve">  isNotAuthorized: 'Найти ранее скрытую карту можно в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru) . Для этого зайдите в раздел «Скрытые продукты» на главной странице.'</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Оплата товаров и услуг доступна на главном экране в разделе «Платежи» [«Уралсиб Онлайн»](https://uralsib.ru/online).'</t>
+          <t xml:space="preserve">  isNotAuthorized: 'Найти ранее скрытую карту можно в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru). Для этого зайдите в раздел «Скрытые продукты» на главной странице.'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед точкой</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22</v>
+        <v>157</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isAuthorized: 'Оплата товаров и услуг доступна на главном экране в разделе [«Платежи»]({{$temp.PaymentsLink}})'</t>
+          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) : выберите продукт -&gt; «Управление» -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isAuthorized: 'Оплата товаров и услуг доступна на главном экране в разделе [«Платежи»]({{$temp.PaymentsLink}}).'</t>
+          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите продукт -&gt; «Управление» -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед двоеточием</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Чтобы сделать перевод, внизу главной страницы нажмите кнопку «Платежи» [«Уралсиб Онлайн»](https://uralsib.ru/online)'</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Чтобы сделать перевод, внизу главной страницы нажмите кнопку «Платежи» [«Уралсиб Онлайн»](https://uralsib.ru/online).'</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед двоеточием</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isAuthorized: 'Чтобы сделать перевод, внизу главной страницы перейдите в раздел [«Платежи»]({{$temp.PaymentsLink}})'</t>
+          <t xml:space="preserve">      3. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isAuthorized: 'Чтобы сделать перевод, внизу главной страницы перейдите в раздел [«Платежи»]({{$temp.PaymentsLink}}).'</t>
+          <t xml:space="preserve">      3. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлена запятая — для единообразия с аналогичным пунктом в файле (стр. 260), где запятая есть</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Найти ранее скрытую карту можно в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru) . Для этого зайдите в раздел «Скрытые продукты» на главной странице.'</t>
+          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) : выберите карту -&gt; «Управление» -&gt; «Заблокировать».</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: 'Найти ранее скрытую карту можно в приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru). Для этого зайдите в раздел «Скрытые продукты» на главной странице.'</t>
+          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите карту -&gt; «Управление» -&gt; «Заблокировать».</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед точкой</t>
+          <t>убран лишний пробел перед двоеточием</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ManageCardsTopUpLink: Вы можете пополнить вашу карту по [ссылке]({{$temp.DBOCardTopUpLink}})</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите карту, внизу страницы «Действия» -&gt; «Заблокировать».</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ManageCardsTopUpLink: Вы можете пополнить вашу карту по [ссылке]({{$temp.DBOCardTopUpLink}}).</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите карту, внизу страницы «Действия» -&gt; «Заблокировать».</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед двоеточием</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) : выберите продукт -&gt; «Управление» -&gt; «Выписка и справки».</t>
+          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите продукт -&gt; «Управление» -&gt; «Выписка и справки».</t>
+          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед двоеточием</t>
+          <t>добавлена запятая, ср. со стр. 260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите карту, внизу страницы «Действия» -&gt; «Разблокировать».</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите карту, внизу страницы «Действия» -&gt; «Разблокировать».</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -610,559 +610,239 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">      3. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">      3. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>добавлена запятая — для единообразия с аналогичным пунктом в файле (стр. 260), где запятая есть</t>
+          <t>добавлена запятая, ср. со стр. 260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ManageCardsStatementLink: Заказать выписку по вашей карте можно по [ссылке]({{$temp.DBOCardStatementLink}})</t>
+          <t xml:space="preserve">          3. В [банкомате Уралсиба]({{$temp.ATMLink}}) Для этого нужно ввести действующий ПИН-код.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ManageCardsStatementLink: Заказать выписку по вашей карте можно по [ссылке]({{$temp.DBOCardStatementLink}}).</t>
+          <t xml:space="preserve">          3. В [банкомате Уралсиба]({{$temp.ATMLink}}). Для этого нужно ввести действующий ПИН-код.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлена точка — два предложения были слиты без разделителя</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online) : выберите карту -&gt; «Управление» -&gt; «Заблокировать».</t>
+          <t xml:space="preserve">    - Если карта выдавалась с ПИН-конвертом, то изменить ПИН-код можно только в [банкомате Уралсиба]({{$temp.ATMLink}}) Для этого нужно ввести действующий ПИН-код. Если забыли ПИН-код, вам потребуется перевыпуск карты.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите карту -&gt; «Управление» -&gt; «Заблокировать».</t>
+          <t xml:space="preserve">    - Если карта выдавалась с ПИН-конвертом, то изменить ПИН-код можно только в [банкомате Уралсиба]({{$temp.ATMLink}}). Для этого нужно ввести действующий ПИН-код. Если забыли ПИН-код, вам потребуется перевыпуск карты.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед двоеточием</t>
+          <t>добавлена точка — два предложения были слиты без разделителя</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>178</v>
+        <v>340</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите карту, внизу страницы «Действия» -&gt; «Заблокировать».</t>
+          <t xml:space="preserve">       2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите карту, внизу страницы «Действия» -&gt; «Заблокировать».</t>
+          <t xml:space="preserve">       2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед двоеточием</t>
+          <t>эн-дефис в стрелке-разделителе заменён на дефис</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>180</v>
+        <v>426</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">          2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите счет  -&gt; «Информация».</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">          2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите счет -&gt; «Информация».</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>добавлена запятая, ср. со стр. 260</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>199</v>
+        <v>471</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) : на главной странице выберите карту, внизу страницы «Действия» -&gt; «Разблокировать».</t>
+          <t xml:space="preserve">           2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия»  -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите карту, внизу страницы «Действия» -&gt; «Разблокировать».</t>
+          <t xml:space="preserve">           2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед двоеточием</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>201</v>
+        <v>577</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}) при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">        1. На главной странице нажимте «Кредиты», выберите нужный кредит</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      4. В [офисе банка]({{$temp.OfficeLink}}), при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">        1. На главной странице нажмите «Кредиты», выберите нужный кредит</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>добавлена запятая, ср. со стр. 260</t>
+          <t>опечатка «нажимте» → «нажмите»</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>212</v>
+        <v>578</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">          3. В [банкомате Уралсиба]({{$temp.ATMLink}}) Для этого нужно ввести действующий ПИН-код.</t>
+          <t xml:space="preserve">        2. Войдите на вкладку «Информация» - «Условия обслуживания»</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">          3. В [банкомате Уралсиба]({{$temp.ATMLink}}). Для этого нужно ввести действующий ПИН-код.</t>
+          <t xml:space="preserve">        2. Войдите на вкладку «Информация» — «Условия обслуживания»</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>добавлена точка — два предложения были слиты без разделителя</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>213</v>
+        <v>594</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Если карта выдавалась с ПИН-конвертом, то изменить ПИН-код можно только в [банкомате Уралсиба]({{$temp.ATMLink}}) Для этого нужно ввести действующий ПИН-код. Если забыли ПИН-код, вам потребуется перевыпуск карты.</t>
+          <t xml:space="preserve">            1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите нужный продукт -&gt;раздел «О кредите» -&gt; «Условия обслуживания».</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Если карта выдавалась с ПИН-конвертом, то изменить ПИН-код можно только в [банкомате Уралсиба]({{$temp.ATMLink}}). Для этого нужно ввести действующий ПИН-код. Если забыли ПИН-код, вам потребуется перевыпуск карты.</t>
+          <t xml:space="preserve">            1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите нужный продукт -&gt; раздел «О кредите» -&gt; «Условия обслуживания».</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>добавлена точка — два предложения были слиты без разделителя</t>
+          <t>добавлен пробел после стрелки-разделителя</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>318</v>
+        <v>631</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">        3. В [банкомате Уралсиба]({{$temp.ATMLink}})</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) а главном экране нажмите на раздел «Еще», или значок человека в правом верхнем углу, если используете личный компьютер -&gt; раздел «Настройки СБП»</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">        3. В [банкомате Уралсиба]({{$temp.ATMLink}}).</t>
+          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) на главном экране нажмите на раздел «Еще», или значок человека в правом верхнем углу, если используете личный компьютер -&gt; раздел «Настройки СБП»</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>опечатка «а» → «на» (пропущена буква)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>332</v>
+        <v>657</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Настроить их можно по [ссылке]({{$temp.DBOCardNotificationsOnLink}})</t>
+          <t xml:space="preserve">    Чтобы настроить подтверждение операций по «Touch ID», «Face ID» и «короткому коду» в [«Уралсиб Онлайн»](https://uralsib.ru/online)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Настроить их можно по [ссылке]({{$temp.DBOCardNotificationsOnLink}}).</t>
+          <t xml:space="preserve">    Чтобы настроить подтверждение операций по «Touch ID», «Face ID» и «короткому коду» в [«Уралсиб Онлайн»](https://uralsib.ru/online):</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлено двоеточие перед списком шагов — для единообразия с аналогичным пунктом в файле (стр. 661), где двоеточие есть</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>340</v>
+        <v>719</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">       2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
+          <t xml:space="preserve">  start: Если суммарный баланс всех банковских продуктов от 100 тысяч рублей, то сброс пароля не сработает - для смены пароля обратитесь по номеру 8-800-250-57-57 или в офис.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">       2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">  start: Если суммарный баланс всех банковских продуктов от 100 тысяч рублей, то сброс пароля не сработает — для смены пароля обратитесь по номеру 8-800-250-57-57 или в офис.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>эн-дефис в стрелке-разделителе заменён на дефис; добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>352</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ManageCardsUralsibBonusLink: Посмотреть баланс бонусного счета и узнать подробности о программе лояльности вы можете по [ссылке]({{$temp.DBOCardBonusLink}})</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ManageCardsUralsibBonusLink: Посмотреть баланс бонусного счета и узнать подробности о программе лояльности вы можете по [ссылке]({{$temp.DBOCardBonusLink}}).</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>404</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SavingsTopUpLink: Пополните выбранный счет по [ссылке]({{$temp.DBODepositTopUpLink}})</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SavingsTopUpLink: Пополните выбранный счет по [ссылке]({{$temp.DBODepositTopUpLink}}).</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>426</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите счет  -&gt; «Информация».</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите счет -&gt; «Информация».</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>убран двойной пробел</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>432</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SavingsDetailsLink: Узнать реквизиты выбранного счета можно по [ссылке]({{$temp.DBODepositDetailsLink}})</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SavingsDetailsLink: Узнать реквизиты выбранного счета можно по [ссылке]({{$temp.DBODepositDetailsLink}}).</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>471</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия»  -&gt; «Выписка и справки».</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           2. В [веб-версии на сайте](https://online.uralsib.ru): на главной странице выберите продукт, внизу страницы «Действия» -&gt; «Выписка и справки».</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>убран двойной пробел</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>477</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SavingsStatementLink: Заказать выписку по выбранному счету можно по [ссылке]({{$temp.DBODepositStatementLink}})</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SavingsStatementLink: Заказать выписку по выбранному счету можно по [ссылке]({{$temp.DBODepositStatementLink}}).</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>527</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LoansDetailsLink: Получить реквизиты выбранного кредита вы можете по [ссылке]({{$temp.DBOLoanDetailsLink}}) </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LoansDetailsLink: Получить реквизиты выбранного кредита вы можете по [ссылке]({{$temp.DBOLoanDetailsLink}}). </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>545</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LoansEarlyRepaymentLink: Для досрочного погашения выбранного кредита перейдите по [ссылке]({{$temp.DBOLoanEarlyRepaymentLink}})</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LoansEarlyRepaymentLink: Для досрочного погашения выбранного кредита перейдите по [ссылке]({{$temp.DBOLoanEarlyRepaymentLink}}).</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>571</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LoansTopUpLink: Для погашения выбранного кредита перейдите по [ссылке]({{$temp.DBOLoanTopUpLink}})</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LoansTopUpLink: Для погашения выбранного кредита перейдите по [ссылке]({{$temp.DBOLoanTopUpLink}}).</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>577</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        1. На главной странице нажимте «Кредиты», выберите нужный кредит</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        1. На главной странице нажмите «Кредиты», выберите нужный кредит</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>опечатка «нажимте» → «нажмите»</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>578</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        2. Войдите на вкладку «Информация» - «Условия обслуживания»</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        2. Войдите на вкладку «Информация» — «Условия обслуживания»</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>594</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите нужный продукт -&gt;раздел «О кредите» -&gt; «Условия обслуживания».</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            1. В приложении [«Уралсиб Онлайн»](https://uralsib.ru/online): выберите нужный продукт -&gt; раздел «О кредите» -&gt; «Условия обслуживания».</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>добавлен пробел после стрелки-разделителя</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>601</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>LoansTermsLink: Чтобы ознакомиться с условиями выбранного кредита, перейдите по [ссылке]({{$temp.DBOLoanTermsLink}})</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LoansTermsLink: Чтобы ознакомиться с условиями выбранного кредита, перейдите по [ссылке]({{$temp.DBOLoanTermsLink}}).</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>631</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) а главном экране нажмите на раздел «Еще», или значок человека в правом верхнем углу, если используете личный компьютер -&gt; раздел «Настройки СБП»</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      2. В [веб-версии на сайте](https://online.uralsib.ru) на главном экране нажмите на раздел «Еще», или значок человека в правом верхнем углу, если используете личный компьютер -&gt; раздел «Настройки СБП»</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>опечатка «а» → «на» (пропущена буква)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>657</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Чтобы настроить подтверждение операций по «Touch ID», «Face ID» и «короткому коду» в [«Уралсиб Онлайн»](https://uralsib.ru/online)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Чтобы настроить подтверждение операций по «Touch ID», «Face ID» и «короткому коду» в [«Уралсиб Онлайн»](https://uralsib.ru/online):</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>добавлено двоеточие перед списком шагов — для единообразия с аналогичным пунктом в файле (стр. 661), где двоеточие есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>719</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start: Если суммарный баланс всех банковских продуктов от 100 тысяч рублей, то сброс пароля не сработает - для смены пароля обратитесь по номеру 8-800-250-57-57 или в офис.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  start: Если суммарный баланс всех банковских продуктов от 100 тысяч рублей, то сброс пароля не сработает — для смены пароля обратитесь по номеру 8-800-250-57-57 или в офис.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
         <is>
           <t>дефис заменён на тире</t>
         </is>
